--- a/MED01S.xlsx
+++ b/MED01S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="401">
   <si>
     <t/>
   </si>
@@ -736,7 +736,7 @@
     <t>20141639</t>
   </si>
   <si>
-    <t>SKTONIK ACTV GUMMY6S</t>
+    <t>SAKATONIK AC GM 24 G</t>
   </si>
   <si>
     <t>10000073</t>
@@ -1088,12 +1088,6 @@
   </si>
   <si>
     <t>C/LANG TELONLANG 60</t>
-  </si>
-  <si>
-    <t>20134841</t>
-  </si>
-  <si>
-    <t>CUSSONS TELON PLS 60</t>
   </si>
   <si>
     <t>10002941</t>
@@ -1612,7 +1606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F184"/>
+  <dimension ref="A1:F183"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4877,10 +4871,10 @@
         <v>26</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -4897,7 +4891,7 @@
         <v>26</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>46</v>
@@ -4917,7 +4911,7 @@
         <v>26</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>46</v>
@@ -4937,7 +4931,7 @@
         <v>26</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>46</v>
@@ -4957,7 +4951,7 @@
         <v>26</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>46</v>
@@ -4977,10 +4971,10 @@
         <v>26</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -4997,7 +4991,7 @@
         <v>26</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>20</v>
@@ -5017,10 +5011,10 @@
         <v>26</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5037,10 +5031,10 @@
         <v>26</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>46</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5057,10 +5051,10 @@
         <v>26</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5074,13 +5068,13 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5097,10 +5091,10 @@
         <v>29</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -5117,10 +5111,10 @@
         <v>29</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5137,10 +5131,10 @@
         <v>29</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5157,10 +5151,10 @@
         <v>29</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5177,7 +5171,7 @@
         <v>29</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>12</v>
@@ -5197,10 +5191,10 @@
         <v>29</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5217,7 +5211,7 @@
         <v>29</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>20</v>
@@ -5237,7 +5231,7 @@
         <v>29</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>20</v>
@@ -5257,10 +5251,10 @@
         <v>29</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -5277,29 +5271,9 @@
         <v>29</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A184" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F184" s="1" t="s">
         <v>98</v>
       </c>
     </row>

--- a/MED01S.xlsx
+++ b/MED01S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="403">
   <si>
     <t/>
   </si>
@@ -503,6 +503,12 @@
   </si>
   <si>
     <t>LASERIN O/BATUK 110M</t>
+  </si>
+  <si>
+    <t>10000680</t>
+  </si>
+  <si>
+    <t>NELLCO OBH SPCL  100</t>
   </si>
   <si>
     <t>20006531</t>
@@ -1606,7 +1612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F183"/>
+  <dimension ref="A1:F184"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2971,10 +2977,10 @@
         <v>15</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2991,10 +2997,10 @@
         <v>15</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -3011,10 +3017,10 @@
         <v>15</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3031,10 +3037,10 @@
         <v>15</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -3048,13 +3054,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3071,7 +3077,7 @@
         <v>19</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -3091,7 +3097,7 @@
         <v>19</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -3111,7 +3117,7 @@
         <v>19</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -3131,7 +3137,7 @@
         <v>19</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -3151,7 +3157,7 @@
         <v>19</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3171,7 +3177,7 @@
         <v>19</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3191,7 +3197,7 @@
         <v>19</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3211,7 +3217,7 @@
         <v>19</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3231,7 +3237,7 @@
         <v>19</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3251,7 +3257,7 @@
         <v>19</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3271,7 +3277,7 @@
         <v>19</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3291,10 +3297,10 @@
         <v>19</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>123</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3311,7 +3317,7 @@
         <v>19</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>123</v>
@@ -3331,7 +3337,7 @@
         <v>19</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>123</v>
@@ -3351,10 +3357,10 @@
         <v>19</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>20</v>
+        <v>123</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3371,7 +3377,7 @@
         <v>19</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>20</v>
@@ -3391,7 +3397,7 @@
         <v>19</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>20</v>
@@ -3411,10 +3417,10 @@
         <v>19</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3431,18 +3437,18 @@
         <v>19</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>212</v>
+        <v>65</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>214</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3451,18 +3457,18 @@
         <v>19</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>46</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>217</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3471,18 +3477,18 @@
         <v>19</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>220</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3491,30 +3497,30 @@
         <v>19</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>123</v>
+        <v>33</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="C95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F95" s="1" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3534,7 +3540,7 @@
         <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3554,7 +3560,7 @@
         <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3574,7 +3580,7 @@
         <v>4</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3611,10 +3617,10 @@
         <v>23</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>123</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3634,7 +3640,7 @@
         <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>20</v>
+        <v>123</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3654,7 +3660,7 @@
         <v>8</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3694,7 +3700,7 @@
         <v>8</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3711,10 +3717,10 @@
         <v>23</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3734,7 +3740,7 @@
         <v>11</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>140</v>
+        <v>98</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3774,7 +3780,7 @@
         <v>11</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3794,7 +3800,7 @@
         <v>11</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>20</v>
+        <v>123</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3811,7 +3817,7 @@
         <v>23</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>20</v>
@@ -3834,7 +3840,7 @@
         <v>15</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>123</v>
+        <v>20</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3854,7 +3860,7 @@
         <v>15</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3874,7 +3880,7 @@
         <v>15</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>123</v>
+        <v>16</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3894,7 +3900,7 @@
         <v>15</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3911,10 +3917,10 @@
         <v>23</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3954,7 +3960,7 @@
         <v>19</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3974,7 +3980,7 @@
         <v>19</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>143</v>
+        <v>53</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3994,7 +4000,7 @@
         <v>19</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>20</v>
+        <v>143</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4011,7 +4017,7 @@
         <v>23</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>20</v>
@@ -4034,7 +4040,7 @@
         <v>23</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4054,7 +4060,7 @@
         <v>23</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4074,7 +4080,7 @@
         <v>23</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4094,7 +4100,7 @@
         <v>23</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4111,10 +4117,10 @@
         <v>23</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4134,7 +4140,7 @@
         <v>26</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4154,7 +4160,7 @@
         <v>26</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>140</v>
+        <v>46</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4174,7 +4180,7 @@
         <v>26</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>20</v>
+        <v>140</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4211,10 +4217,10 @@
         <v>23</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4234,7 +4240,7 @@
         <v>29</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4254,7 +4260,7 @@
         <v>29</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4274,7 +4280,7 @@
         <v>29</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4311,7 +4317,7 @@
         <v>23</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>20</v>
@@ -4334,7 +4340,7 @@
         <v>32</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4354,7 +4360,7 @@
         <v>32</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4374,7 +4380,7 @@
         <v>32</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4394,7 +4400,7 @@
         <v>32</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4411,7 +4417,7 @@
         <v>23</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>20</v>
@@ -4434,7 +4440,7 @@
         <v>36</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4454,7 +4460,7 @@
         <v>36</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4474,7 +4480,7 @@
         <v>36</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4494,7 +4500,7 @@
         <v>36</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4511,10 +4517,10 @@
         <v>23</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4534,7 +4540,7 @@
         <v>39</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4554,7 +4560,7 @@
         <v>39</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4571,10 +4577,10 @@
         <v>23</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>98</v>
+        <v>12</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4594,7 +4600,7 @@
         <v>42</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4631,10 +4637,10 @@
         <v>23</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>123</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4654,7 +4660,7 @@
         <v>45</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4671,10 +4677,10 @@
         <v>23</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -4711,10 +4717,10 @@
         <v>23</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>123</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4734,7 +4740,7 @@
         <v>52</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4751,10 +4757,10 @@
         <v>23</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -4774,27 +4780,27 @@
         <v>56</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>350</v>
+        <v>20</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B159" s="1" t="s">
+      <c r="C159" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F159" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F159" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4808,13 +4814,13 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4831,7 +4837,7 @@
         <v>26</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>46</v>
@@ -4851,10 +4857,10 @@
         <v>26</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4871,10 +4877,10 @@
         <v>26</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -4891,7 +4897,7 @@
         <v>26</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>46</v>
@@ -4911,7 +4917,7 @@
         <v>26</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>46</v>
@@ -4931,7 +4937,7 @@
         <v>26</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>46</v>
@@ -4951,7 +4957,7 @@
         <v>26</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>46</v>
@@ -4971,10 +4977,10 @@
         <v>26</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -4991,7 +4997,7 @@
         <v>26</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>20</v>
@@ -5011,10 +5017,10 @@
         <v>26</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5031,10 +5037,10 @@
         <v>26</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5051,10 +5057,10 @@
         <v>26</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5068,13 +5074,13 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5091,10 +5097,10 @@
         <v>29</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -5111,10 +5117,10 @@
         <v>29</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5131,10 +5137,10 @@
         <v>29</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5151,10 +5157,10 @@
         <v>29</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5171,7 +5177,7 @@
         <v>29</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>12</v>
@@ -5191,10 +5197,10 @@
         <v>29</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5211,7 +5217,7 @@
         <v>29</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>20</v>
@@ -5231,7 +5237,7 @@
         <v>29</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>20</v>
@@ -5251,10 +5257,10 @@
         <v>29</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -5271,9 +5277,29 @@
         <v>29</v>
       </c>
       <c r="E183" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E184" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F183" s="1" t="s">
+      <c r="F184" s="1" t="s">
         <v>98</v>
       </c>
     </row>

--- a/MED01S.xlsx
+++ b/MED01S.xlsx
@@ -1099,7 +1099,7 @@
     <t>10002941</t>
   </si>
   <si>
-    <t>C/LANG KAYU PUTIH120</t>
+    <t>C.LANG KY PTH 120 ML</t>
   </si>
   <si>
     <t>10000425</t>
@@ -1159,13 +1159,13 @@
     <t>20046056</t>
   </si>
   <si>
-    <t>MY BABY TLN PLUS 150</t>
+    <t>MY BABY TLN+ 150 ML</t>
   </si>
   <si>
     <t>20125042</t>
   </si>
   <si>
-    <t>MYBABY TLN PLS LV150</t>
+    <t>MY BABY TLN L 150 ML</t>
   </si>
   <si>
     <t>20037413</t>

--- a/MED01S.xlsx
+++ b/MED01S.xlsx
@@ -538,7 +538,7 @@
     <t>20139611</t>
   </si>
   <si>
-    <t>FCARE STRONG 15+5ML</t>
+    <t>FRSH/C STRONG 15+5ML</t>
   </si>
   <si>
     <t>20040719</t>
@@ -838,7 +838,7 @@
     <t>10000452</t>
   </si>
   <si>
-    <t>ULTRA FLU 4'S</t>
+    <t>ULTRA FLU PE 4S</t>
   </si>
   <si>
     <t>10000555</t>
